--- a/text/foundationScores/shapesphysical_3_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/shapesphysical_3_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AI59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,34 +604,38 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.175</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>82</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>18</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>2.58</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Let's all go to the lobby.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -632,66 +646,72 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.1694915254237288</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.1236559139784946</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.1185567010309278</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.0891089108910891</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.1036585365853658</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.4142857142857143</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.2467532467532468</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.1458333333333333</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.2533333333333334</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.1463414634146341</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
       <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10.544</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.656</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>44.04</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Let's all go to the lobby.  Let's all go to the lobby to get ourselves a treat.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.1016949152542373</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.0909090909090909</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.02898550724637681</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.04700854700854701</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.1129943502824859</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.08243727598566308</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.07903780068728523</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.0594059405940594</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.06910569105691056</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>1.5</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0857142857142857</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.1159420289855072</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.3274725274725275</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.07971014492753624</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.2542457542457542</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.1849415204678363</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>0.02857142857142857</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>0.1688888888888889</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.1515151515151515</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0.09756097560975609</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
       <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0.04830917874396135</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -804,104 +834,114 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16.992</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12.166</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>31.6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>57.19</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Delicious things to eat.  The popcorn can't be beat.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.07751937984496123</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.03846153846153847</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.07109799838019205</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.02729885057471264</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.1122073447654843</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.05061250805931657</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.01801801801801802</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.06346826586706646</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.13955463728191</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>1.5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.06832298136645963</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.06725146198830409</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.1</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>0.1606263982102908</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.06521739130434782</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>0.1497524752475247</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>0.08</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>0.07777777777777778</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>0.05921052631578947</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
         <v>0.125</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -909,34 +949,38 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>22.399</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17.012</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>83.3</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>16.7</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>29.6</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">  The sparkling drinks are just dandy.  The chocolate bars and the candy.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -971,14 +1015,14 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.2592592592592592</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
@@ -986,27 +1030,33 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.2380952380952381</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.1904761904761905</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
       <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1014,34 +1064,38 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26.224</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>22.419</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>10.9</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>2.58</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve"> So let's all go to the lobby to get ourselves</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
@@ -1052,66 +1106,72 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.1694915254237288</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.1236559139784946</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.1185567010309278</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.0891089108910891</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.1036585365853658</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
         <v>0.4142857142857143</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.2467532467532468</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.1458333333333333</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
         <v>0.2533333333333334</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
         <v>0.1463414634146341</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
       <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>49.077</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30.811</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>84.7</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>15.3</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>40.19</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve"> To get ourselves a treat A small triangle overlapping a smaller circle slides into a rectangle.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.1525423728813559</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.1363636363636364</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.09580384226491405</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.07051282051282051</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.04770318021201414</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.04104477611940299</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.05384615384615385</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.04028436018957346</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.1285714285714286</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.1739130434782609</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.1195652173913044</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.2160107334525939</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.09854014598540146</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>0.04777070063694268</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.076</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>0.05038759689922481</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
         <v>0.03365384615384615</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.055</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1224,33 +1294,37 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>54.646</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>49.758</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangle touches the circle which glides away.  The triangle slides to it and the circle moves away.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.02185792349726776</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0.02185792349726776</v>
@@ -1259,69 +1333,75 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.02185792349726776</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.05583756345177665</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.09640646232825005</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.08013640238704177</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.1264734299516908</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.06632633329465908</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>0.02976190476190476</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.04901960784313725</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>0.08888888888888889</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.1468834688346884</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>0.2071005917159764</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.1444444444444445</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.09977324263038549</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.1360544217687075</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0.1238938053097345</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>61.657</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>54.766</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>100</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve"> The triangle comes into contact with the circle again and the circle ricochets between the side of the rectangle and the triangle several times.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.03660767189633408</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.0258751902587519</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.03345189701897019</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.01657458563535912</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.02973720608575381</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.07884447262491474</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.04166415193031162</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.02113156100886163</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.02340425531914894</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>0.5</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.03418803418803418</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>0.1295432962099629</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>0.06306306306306307</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.02845528455284553</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0.08466922555881688</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>0.1212121212121212</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>0.03185185185185185</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.06393387314439945</v>
       </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
         <v>0.05922865013774106</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.06451330532212884</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.04238085635544801</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.03809523809523809</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1434,33 +1524,37 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>66.184</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>62.678</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>100</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve"> The triangle moves in a ring around the circle, rotating.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.06557377049180327</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0.06557377049180327</v>
@@ -1469,56 +1563,56 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.06557377049180327</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>0.1216216216216217</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.1594202898550725</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.0392156862745098</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.25</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
         <v>0.08928571428571429</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
       <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.103448275862069</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
@@ -1532,6 +1626,12 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1539,104 +1639,114 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>73.751</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>66.62</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>100</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">  A large triangle slides towards the rectangle.  The small triangle slides outside the rectangle until it is adjacent to the large triangle.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.05268073750606501</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.04123711340206185</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.03294573643410853</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.02385159010600707</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.02722736890261337</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.03473557692307692</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.04207920792079208</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.05999245009969591</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.5</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.00819672131147541</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
         <v>0.008333333333333333</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.04069767441860465</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
         <v>0.09627862000124773</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>0.09196344362475938</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
         <v>0.1273344244408074</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>0.04978396238403864</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.08055555555555555</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.03026778329197684</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.09907939189189188</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>81.723</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>73.771</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>93.30000000000001</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>6.7</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>20.23</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">  After bouncing, both triangles slide out of the scene.  The rectangle reassembles into a square-like structure with a triangular top and a line in the middle.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.001954887218045113</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.02491720662347012</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.01587018467361277</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.001299638989169675</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.00242914979757085</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.05790312858503956</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.0458664699786195</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.04602890590584023</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.03833070532774983</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.03699228552839483</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.01543637062668205</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.02272540376961284</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.004629629629629629</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.002471169686985173</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.04680933852140078</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>0.02825459317585302</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.01164001332667</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>0.08786953201701755</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>0.07951587714731911</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>0.06865382042017931</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>0.1104075866422195</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.08148148148148147</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.03472222222222222</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.05793905372894948</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1749,67 +1869,71 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>87.713</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>81.843</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>100</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangles slide into the structure through a gap in the bottom.  The triangles rotate 90 degrees.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.07916666666666666</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0.0588235294117647</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>0.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
@@ -1847,6 +1971,12 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>92.56</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>88.073</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>89</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>11</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>-15.31</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve"> The small triangle slides diagonally to the upper right, stopping at the middle line.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.03079847908745247</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.03387622149837134</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.05493242389794114</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.09310662849722583</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.08381552021443725</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.07992413197917572</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.05525967513660945</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.02857460776677422</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.05959032545022218</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>1.25</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.07804101838755303</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.04883720930232558</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.1257620521010081</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.02333333333333333</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.04151542649727767</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>0.1371396050097183</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.05928358040696691</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>0.08998715375351264</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>0.07677785568006718</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.08884196297870331</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.06819767441860465</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1959,104 +2099,114 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>102.871</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>93.839</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>85.2</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>14.8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>48.65</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle does the same.  The triangles rotate so their top corners touch and then the small triangle rotates so the top corner points up.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.02361111111111111</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.07155687307861221</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.02061855670103093</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.05500894454382827</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>0.03101503759398496</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0.05737166480255235</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.02052238805970149</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>0.04826732673267327</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.03947207700200323</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.0272108843537415</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
         <v>0.02325581395348837</v>
       </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>0.05426356589147287</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>0.08056724326009039</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
         <v>0.09703246199596564</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>0.1026254450824916</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>0.101948717948718</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>0.07776295166687847</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>0.066005291005291</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>0.02243589743589744</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AH15" t="n">
         <v>0.09475332475332476</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -2064,104 +2214,114 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>107.176</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>103.532</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>100</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve"> The large triangle slides diagonally down and rotates in place.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.04722222222222222</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.081906969861392</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.04130434782608695</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.05125</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.04606741573033708</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.04914529914529914</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.04207920792079208</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.03865979381443298</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>0.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
         <v>0.06511627906976744</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>0.08536585365853659</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>0.1208508648901356</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
         <v>0.1129426129426129</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>0.05514705882352941</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>0.1460720130932897</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>0.06664623870078137</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>0.07222222222222222</v>
       </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0.1198488811392037</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2169,34 +2329,38 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>110.981</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>107.417</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>100</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve"> Both triangles move slightly, up and down, up and down.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -2267,6 +2431,12 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2274,104 +2444,114 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>116.809</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>111.342</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>89.3</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>10.7</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>20.23</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve"> The top of the structure rotates open and the small triangle moves slowly upwards while rotating.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.04121613765841181</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.06218553459119497</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.06204277008396736</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.02616279069767442</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.02385159010600707</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.05092779346510691</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.02692307692307692</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.07945883228874177</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.05375562547293799</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.06086956521739131</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.08761314443132624</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.101797385620915</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>0.05426356589147287</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>0.04487594390507012</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>0.07084639498432602</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>0.1426165075800112</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>0.03184713375796178</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>0.05066666666666667</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>0.07840965843701821</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AG18" t="n">
         <v>0.02243589743589744</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AH18" t="n">
         <v>0.03666666666666667</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2379,43 +2559,47 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>127.695</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>123.37</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>100</v>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">  The structure turns into a large V.  The branches of the V rotate up and down.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.04722222222222222</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.1088383838383838</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.07349517791819088</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2426,20 +2610,20 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.06646945182323111</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.08627884143348061</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.4</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -2450,33 +2634,39 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.1449275362318841</v>
       </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>0.09401709401709402</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>0.1102941176470588</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.04918032786885246</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>0.1444444444444444</v>
       </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.1171171171171171</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -2484,104 +2674,114 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>145.036</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>127.775</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>100</v>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve"> The V splits into two smaller Vs and the triangle moves left and right with the Vs. Again, the two Vs split in half, making four Vs. The four Vs move in the same direction as the triangle, which moves left and right.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.06116248679102387</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.06703740463588091</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.08439373678020441</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.06401776625325929</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.01052631578947368</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.0485724879495736</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.05418136340829608</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.03807526061530638</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.05548093162091042</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.06297766161484698</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0.1253543962859269</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
         <v>0.1118818681318681</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>0.1002262443438914</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>0.1313578861727505</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>0.04506437768240344</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>0.07727272727272727</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>0.07205467814804803</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>0.09463812050018947</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.07946993029664451</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>0.06969987228607918</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0.08631629591894494</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
         <v>0.06854281767955801</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>0.05054525627044711</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2589,104 +2789,114 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>148.821</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>145.677</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>72.3</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>27.7</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>31.82</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Vs reform the original square-like structure.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0396612448748652</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.07696264461271538</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.05302332171774291</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.04900655463616711</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>0.04006374817133331</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.01219512195121951</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.1134892287085612</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.08337798735398136</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.009259259259259259</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.02417310860473958</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>0.01361867704280156</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.00984251968503937</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>0.006038647342995169</v>
       </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
       <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AH21" t="n">
         <v>0.02941176470588235</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2694,104 +2904,114 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>153.292</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>149.628</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>100</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve"> The big triangle appears and the triangles move slightly up and down.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.05141843971631206</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.02727272727272727</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.03738317757009346</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.08346017250126839</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.0460470984020185</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.03658536585365853</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.0456081081081081</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.04356060606060606</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.0847457627118644</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>0.08181818181818182</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.07722122838401908</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.1063241106719368</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.06778309409888357</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>0.05128205128205128</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>0.06504065040650407</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.05214723926380368</v>
       </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
         <v>0.03968253968253968</v>
       </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
       <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0.01428571428571429</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2799,104 +3019,114 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>161.902</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>154.634</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>100</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">  The big triangle moves diagonally up to the middle line.  Adjacent to the little triangle, it moves up and down once.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.03899740340270511</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.03696903460837887</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.0216848572595315</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>0.01151761517615176</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.04432493215187557</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.09748780645112742</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.04262121335199195</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>0.076952269757336</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.04217672755504284</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>1.5</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
         <v>0.06512258368694013</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>0.06193950448396413</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.02179691653375864</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>0.07044645462503647</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.06768208399787347</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.05732390215148836</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>0.1880048995448091</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.04098123314693161</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>0.0554914358356751</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>0.03438937148696986</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AG23" t="n">
         <v>0.02314814814814815</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AH23" t="n">
         <v>0.03679361869452871</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -2904,104 +3134,114 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>169.471</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>165.827</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>100</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle moves diagonally down.  The small triangle does the same.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.05333940497874923</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.03367003367003366</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.04934933243197567</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.03488372093023256</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.03180212014134276</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.06790372462014255</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.0358974358974359</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.08119290189888555</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.06570133142750756</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
         <v>0.02976190476190476</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.04901960784313725</v>
       </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0.05426356589147287</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.07053140096618359</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>0.1739555389190426</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.06861183964031473</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>0.101948717948718</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>0.0499851738891007</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>0.04814814814814814</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>0.02243589743589744</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.07570570570570571</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3009,67 +3249,71 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>178.521</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>169.751</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>88.8</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>11.2</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>-34</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">  The small triangle slides down out of the structure.  The large triangle disappears and the entire structure rotates 360 degrees.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.01888888888888889</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.06686868686868687</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.04230129697372796</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.02093023255813953</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.04468127208480566</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>0.04080815435020022</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.03753846153846154</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.06248766913994125</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.08676691679085777</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
@@ -3077,36 +3321,42 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>0.05426356589147287</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.09959123002601263</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>0.05303030303030303</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>0.1789996751107198</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>0.1189263050491198</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>0.152263183357523</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>0.08173120563513243</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>0.1124756335282651</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>0.02243589743589744</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>0.07570570570570571</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -3114,104 +3364,114 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>192.599</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>182.669</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>100</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle appears at the bottom.  The small triangle moves into the structure, moves up and down next to the large triangle once, and then slides diagonally up to the middle of the structure.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.03555960331916616</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.05443322109988776</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.05554384531072855</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.02294477940472772</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.002554278416347382</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.02248137404366097</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.03964459188339786</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0182477122406451</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.06755268899517308</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.06039159173968475</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>1.8</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.02421307506053269</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.05878781755726593</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>0.05300581771170006</v>
       </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.03624282694050136</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.08882641386073879</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>0.1486896712607151</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.04516137665257185</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.0710611652498445</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>0.04429712518137928</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>0.05079365079365079</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>0.009615384615384614</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.05325795182938041</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3219,104 +3479,114 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>196.804</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>192.88</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>100</v>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve"> Both triangles rotate 90 degrees and then bounce slowly in place.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>0.08133971291866028</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.08260869565217391</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.1025</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.09213483146067417</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.09829059829059827</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
         <v>0.2</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
         <v>0.1302325581395349</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
       <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>0.1707317073170732</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>0.09677419354838709</v>
       </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
         <v>0.1318681318681319</v>
       </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
         <v>0.1382978723404255</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>0.08411214953271028</v>
       </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
       <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0.1225806451612903</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -3324,73 +3594,77 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>202.69</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>198.806</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>84.5</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>15.5</v>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
         <v>-29.6</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve"> The structure's lower pieces form four Vs that again move up and down.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.05833333333333333</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.05603448275862069</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
         <v>0.05670103092783505</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0811965811965812</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.05743243243243244</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.09761904761904762</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>0.04838709677419355</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
@@ -3398,30 +3672,36 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>0.09615384615384615</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>0.0886691776522285</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>0.04129464285714286</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.1023411371237458</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>0.1556776556776557</v>
       </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -3429,104 +3709,114 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>207.715</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>202.89</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>100</v>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">  The small triangle moves upward.  The Vs are positioned around the triangle moving with it.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.07150331356818974</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.05293136982495137</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.05553268848185498</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0.03401360544217687</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.03180212014134276</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.06790372462014255</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0358974358974359</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.05314009661835748</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.03992813555121891</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.6</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
         <v>0.02976190476190476</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.04901960784313725</v>
       </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>0.0913006029285099</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>0.08326324642556771</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>0.1878142476930056</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>0.104069355980184</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>0.09131707317073172</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>0.07132758032275364</v>
       </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.02243589743589744</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.03666666666666667</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -3534,104 +3824,114 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>218.472</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>213.787</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>89.7</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>10.3</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>-12.8</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">  The Vs become rigid and form separate bars.  Other pieces form four longer lines.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.00375</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.01523809523809524</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.02051282051282051</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.04482758620689655</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.005617977528089888</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>0.08115446059239043</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>0.08573648573648573</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.06135583413417127</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>0.05124971519708361</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.06227013316423589</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>1.25</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.07131927629808986</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.04981400255399477</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.04320987654320987</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.02651515151515152</v>
       </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.03269230769230769</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.04696969696969697</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>0.06575963718820861</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>0.1189186551505392</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>0.02232142857142857</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>0.125355214549588</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>0.1097308488612836</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.08062863221253631</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3639,104 +3939,114 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>221.936</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>218.613</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>100</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve"> The long line on the left has hinges and moves towards the triangle.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.01639344262295082</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.03422053231939164</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.04110274494853221</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.09612297026090129</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>0.08899141701190319</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.05604927799258265</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>0.1203621793886769</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.06805668751064095</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
         <v>0.02232142857142857</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>0.03676470588235294</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.04140127388535032</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0.08865771812080536</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.08951847239518472</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>0.0523521351906828</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>0.1967780335485775</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>0.1281240047105939</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>0.1382852434961452</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>0.07000510986203373</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>0.03973509933774835</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>0.03472222222222222</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>0.07695721640333747</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3744,104 +4054,114 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>232.829</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>226.742</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>100</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangle moves to the upper right while the lines move down.  The lines then move vertically, extending towards the triangle.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.0548915414822664</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.08044051496820226</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.1074948699312747</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.03553299492385787</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>0.03097345132743362</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.03040540540540541</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.07744905742617413</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.06581520072781739</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>0.8</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.1443452380952381</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.08303571428571428</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.07522624434389141</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.1056553911205074</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.04506437768240344</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.06666666666666668</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.1087568058076225</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>0.0576923076923077</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>0.1020408163265306</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>0.03729281767955801</v>
       </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -3849,104 +4169,114 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>237.955</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>232.849</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>100</v>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve"> The moving lines reform the square-like structure and the small triangle moves down to the middle line.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.03080716769390288</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.04104960667186034</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.04511508539698331</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.03103232785076667</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.01922334385846106</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.03710729779973797</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.03859213755991549</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.03069981952033858</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.04736242071318151</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.03921540059777424</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>4.5</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>0.04660147384380697</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.04066857746084329</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>0.02069716775599129</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.02024782260573035</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.05764239535889161</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.03496062992125984</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>0.04954372407292289</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>0.1143651088933859</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>0.08223532761844944</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.1188499195071683</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>0.05253987123626</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>0.04477834612105712</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>0.03713820901320902</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AH33" t="n">
         <v>0.04145177838577292</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>2.666666666666667</v>
       </c>
     </row>
@@ -3954,104 +4284,114 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>247.418</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>242.609</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>100</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve"> The large triangle appears, moves left and then rotates to point diagonally up.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.03200364298724954</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.03111111111111111</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.05636228051672131</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.02037037037037037</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.004597701149425288</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.05271598006017257</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.06205226361231697</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.02242562929061784</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>0.08002100577699212</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.05059286557164059</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.06397349305467057</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.05058441558441559</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.06479638009049773</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.03312101910828025</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.09973510852229386</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>0.03520578420467186</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>0.09451391520357037</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>0.08918069241582857</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>0.06801061007957561</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.05756748852643238</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>0.07467696835908756</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>0.02391304347826087</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.0581453427254954</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -4059,104 +4399,114 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>252.428</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>247.759</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>100</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">  It bounces.  The little triangle rotates 90 degrees and slides diagonally down.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>0.09066666666666667</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.06504065040650407</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>0.0893371757925072</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.1068493150684932</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
       <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>0.08490566037735849</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
         <v>0.07017543859649122</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.1409395973154362</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.1491228070175439</v>
       </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
         <v>0.1849315068493151</v>
       </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
         <v>0.125</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0.05797101449275362</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -4164,104 +4514,114 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>260.844</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>252.768</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>88.2</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>11.8</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
         <v>-34</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">  Both bounce and the little triangle exits the structure.  The large triangle disappears and the structure rotates 360 degrees.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.02361111111111111</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.08358585858585858</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.07554328788382662</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.01626016260162602</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0.0223342939481268</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.02671232876712329</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
         <v>0.04542984786283506</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.08817535962060373</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>0.07046979865771812</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>0.147025171624714</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
         <v>0.1394743004332045</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>0.05514705882352941</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>0.1394230769230769</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>0.02459016393442623</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>0.07222222222222222</v>
       </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.08754406580493537</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.2222222222222222</v>
       </c>
     </row>
@@ -4269,104 +4629,114 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>273.611</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>261.084</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>100</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">  The large triangle appears.  The small triangle slides into the structure, bounces adjacent to the large triangle and glides diagonally upwards towards the middle line.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.02698412698412698</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.05331890331890331</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.04346156254009891</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.02950043066322136</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.003284072249589491</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.04931278703572737</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.03224394520251683</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.03947119652614961</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>0.05142433690313107</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.06002418903983615</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>0.02824858757062147</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.03882388238823883</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>0.01282051282051282</v>
       </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
         <v>0.06894996476391825</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.08140859394863971</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>0.005747126436781609</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>0.1227654346788435</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>0.07628709282033087</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>0.1112734871177264</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AE37" t="n">
         <v>0.08080619297050884</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>0.05925925925925925</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>0.03436609686609687</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>0.08926606008001359</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -4374,104 +4744,114 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>279.34</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>275.694</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>100</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve"> It rotates until it points up, as does the large triangle below.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.04722222222222222</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.08311374615722442</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.04123711340206185</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.03529411764705882</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>0.02727272727272727</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.09653465346534654</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.03865979381443298</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.04081632653061224</v>
       </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
         <v>0.03488372093023256</v>
       </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
       <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.1208508648901356</v>
       </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
         <v>0.04700854700854701</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>0.1061674669867947</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>0.06625683060109289</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.0990079365079365</v>
       </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.08712998712998712</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4479,104 +4859,114 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>286.15</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>279.64</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
         <v>9.1</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>20.23</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">  Both bob slightly up and down.  The top of the square-like structure opens and the small triangle moves upwards.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.01883705164550721</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.03114650827933765</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.03623117346496678</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.02778733943413651</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.003036437246963563</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.02385159010600707</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.05092779346510691</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.02692307692307692</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.05205019441498762</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.05375562547293799</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.005767012687427913</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.03696013289036545</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.05519244734931009</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.00329489291598023</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.06334268392000725</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.02878390201224847</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>0.03850852351601976</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>0.1426165075800112</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>0.03184713375796178</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>0.05066666666666667</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AE39" t="n">
         <v>0.03359173126614987</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
         <v>0.02243589743589744</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AH39" t="n">
         <v>0.03666666666666667</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -4584,104 +4974,114 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>297.106</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>288.678</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>100</v>
       </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">  The square forms six lines.  Two have moving parts.  The lines move sideways all together, and a long line with hinges swings out towards the triangle.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.02127659574468085</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.05874587480236584</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.06402016677518864</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.008849557522123892</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.01457725947521866</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.07891248928283211</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.02237056816496069</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.0211118930330753</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.07066389905006969</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.06163385639168906</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>1.4</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.04166666666666667</v>
       </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
       <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
         <v>0.03246753246753246</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>0.06653456908490465</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.06708414872798434</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.08698974776277039</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>0.1085802804916608</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>0.1895621012701799</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>0.2083564555669624</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.09313846362274357</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.09022392220623612</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.03698412698412699</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>0.03803413907664108</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -4689,104 +5089,114 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>304.493</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>297.666</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>100</v>
       </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangle moves downwards.  A small square appears from the left.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>0.01639344262295082</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>0.01363636363636363</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.03508503140799754</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>0.05162575366063737</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>0.00574712643678161</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>0.076627031653526</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>0.08147642189403459</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>0.05495511353634923</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>0.06241604807352422</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>0.05202587374318626</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
         <v>0.0423728813559322</v>
       </c>
-      <c r="T41" t="n">
+      <c r="V41" t="n">
         <v>0.06323051948051948</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>0.05599547511312217</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0.04140127388535032</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>0.06342494714587738</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>0.08843700159489633</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>0.02586206896551724</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>0.1439081934928902</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>0.07916173222801909</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>0.08455172413793104</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>0.04503506829088225</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.03973509933774835</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.01682692307692308</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>0.07090239912758997</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -4794,104 +5204,114 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>312.08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>305.634</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>100</v>
       </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">  Two of the lines rotate to point at them.  The square and the triangle move counterclockwise around the screen.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>0.07301587301587302</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.1279277916446058</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.01754385964912281</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>0.0381416789218848</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>0.0221483942414175</v>
       </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
         <v>0.04715679689136385</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>0.0321009122400254</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>0.75</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.1481046365914787</v>
       </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.05</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.05681818181818182</v>
       </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
         <v>0.05</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>0.08629032258064517</v>
       </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
         <v>0.1592927247234772</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.07964601769911504</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.1219565217391304</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.05978260869565218</v>
       </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -4899,104 +5319,114 @@
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>317.925</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>312.8</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>100</v>
       </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">  The square and triangle move up and down.  The square leaves and re-enters with a small circle.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>0.06319514661274014</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
         <v>0.09487299153276886</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>0.1077114427860696</v>
       </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
         <v>0.1163461538461538</v>
       </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>0.07289305584174738</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>0.4</v>
       </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
         <v>0.1388888888888889</v>
       </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
       <c r="V43" t="n">
         <v>0</v>
       </c>
       <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>0.1950317124735729</v>
       </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
       <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
         <v>0.09854014598540146</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AC43" t="n">
         <v>0.2422151450813871</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>0.1593333333333333</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
         <v>0.1273106738223017</v>
       </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
         <v>0.06698717948717949</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AH43" t="n">
         <v>0.055</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AI43" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -5004,104 +5434,114 @@
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>322.837</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>318.749</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>100</v>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">  The circle is between the triangle and square.  The circle moves quickly towards the lines.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>0.02185792349726776</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>0.0253968253968254</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>0.08817447174152686</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>0.06412722842118763</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>0.06404481404481406</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
         <v>0.1195820636047891</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="S44" t="n">
         <v>0.06272788371909892</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>0.75</v>
       </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
         <v>0.06353648424543946</v>
       </c>
-      <c r="T44" t="n">
+      <c r="V44" t="n">
         <v>0.08609993293091885</v>
       </c>
-      <c r="U44" t="n">
+      <c r="W44" t="n">
         <v>0.09134765017117959</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>0.1142676767676768</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>0.0707070707070707</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Z44" t="n">
         <v>0.05555555555555556</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AA44" t="n">
         <v>0.06781609195402299</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>0.06802721088435375</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>0.1212121212121212</v>
       </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
         <v>0.05797101449275362</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.01388888888888889</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>0.09166666666666667</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AI44" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -5109,104 +5549,114 @@
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>333.838</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>323.057</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>88.7</v>
       </c>
-      <c r="C45" t="n">
+      <c r="E45" t="n">
         <v>11.3</v>
       </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
         <v>-49.39</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve">  When the circle touches the lines, they collapse into pieces.  The triangle moves above the pieces, making a small loop and then glides off the screen.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>0.02472206519690974</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>0.05909829795371965</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>0.08134666083082807</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>0.04378407141417567</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>0.02769423558897243</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>0.06070830246717224</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>0.04702375773490788</v>
       </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
         <v>0.02756410256410257</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>0.05243470996331408</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
         <v>0.0605165214929177</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.1012065347721822</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.02232142857142857</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.08676470588235294</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>0.08064789687924016</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>0.04069767441860465</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Z45" t="n">
         <v>0.07196969696969698</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AA45" t="n">
         <v>0.07745781364636831</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>0.1069623806850084</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>0.1232928552559302</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>0.1289090909090909</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AE45" t="n">
         <v>0.0251937984496124</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AF45" t="n">
         <v>0.1033073206986251</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.01682692307692308</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AH45" t="n">
         <v>0.0275</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AI45" t="n">
         <v>0.4444444444444444</v>
       </c>
     </row>
@@ -5214,104 +5664,114 @@
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>343.969</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>339.623</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>100</v>
       </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">  The pieces are stationary.  The triangle reappears from the bottom left of the screen.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>0.06109725685785537</v>
       </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
         <v>0.05606407322654462</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>0.0451219512195122</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="S46" t="n">
         <v>0.04415954415954416</v>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>0.5</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
         <v>0.1656050955414013</v>
       </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
         <v>0.1477832512315271</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>0.221105527638191</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>0.1862068965517241</v>
       </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
         <v>0.1589403973509934</v>
       </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
         <v>0.1450381679389313</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -5319,34 +5779,38 @@
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>348.294</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>344.529</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>89.3</v>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
         <v>10.7</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
         <v>20.23</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve"> The top of the triangle touches one of the pieces which rotates up and back down.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
@@ -5417,6 +5881,12 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5424,67 +5894,71 @@
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>352.82</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>348.735</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>100</v>
       </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve"> The motion is repeated on another piece and the triangle touches the circle underneath it.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>0.0574712643678161</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
         <v>0.0392156862745098</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>0.08288459507971703</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>0.08039867109634553</v>
       </c>
-      <c r="O48" t="n">
+      <c r="Q48" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="P48" t="n">
+      <c r="R48" t="n">
         <v>0.06345315904139434</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="S48" t="n">
         <v>0.009259259259259259</v>
       </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>0.75</v>
       </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
@@ -5492,36 +5966,42 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
       <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
         <v>0.1176470588235294</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AC48" t="n">
         <v>0.25</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
         <v>0.1904761904761905</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -5529,67 +6009,71 @@
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>357.706</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>353.821</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>100</v>
       </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve"> The circle and triangle moving in sync move up and make a full revolution.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>0.1027699718988358</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>0.06205882352941176</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>0.04661016949152542</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>0.03097345132743362</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>0.0510204081632653</v>
       </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
       <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
         <v>0.07894736842105263</v>
       </c>
-      <c r="P49" t="n">
+      <c r="R49" t="n">
         <v>0.09230769230769233</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="S49" t="n">
         <v>0.01136363636363636</v>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
       <c r="U49" t="n">
         <v>0</v>
       </c>
@@ -5597,36 +6081,42 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
         <v>0.1463414634146341</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AB49" t="n">
         <v>0.1355932203389831</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
         <v>0.2166666666666667</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>0.1219512195121951</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AE49" t="n">
         <v>0.1132075471698113</v>
       </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
       <c r="AF49" t="n">
         <v>0</v>
       </c>
       <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5634,91 +6124,95 @@
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>361.531</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>357.826</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>100</v>
       </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve"> The triangle moves off screen while the circle and the pieces are stationary.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>0.03278688524590163</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.1438979963570127</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
         <v>0.06081081081081083</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
         <v>0.07971014492753623</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="S50" t="n">
         <v>0.0196078431372549</v>
       </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>0.5</v>
       </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
         <v>0.08928571428571429</v>
       </c>
-      <c r="U50" t="n">
+      <c r="W50" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
       <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AA50" t="n">
         <v>0.103448275862069</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
@@ -5732,6 +6226,12 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -5739,104 +6239,114 @@
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>372.345</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>363.754</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>89.3</v>
       </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
         <v>10.7</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
         <v>20.23</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">  The pieces reform the square-like structure.  The small triangle moves slowly into it from the top.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>0.02566566780647199</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>0.04265119677125338</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>0.04205026540513926</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>0.04346880960040655</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>0.01419385567992379</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>0.01908127208480566</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>0.04074223477208553</v>
       </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
         <v>0.02153846153846154</v>
       </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
         <v>0.0416401555319901</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="S51" t="n">
         <v>0.04300450037835039</v>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>1.25</v>
       </c>
-      <c r="S51" t="n">
+      <c r="U51" t="n">
         <v>0.05674461435428062</v>
       </c>
-      <c r="T51" t="n">
+      <c r="V51" t="n">
         <v>0.06401042224841925</v>
       </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
         <v>0.04139433551198257</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>0.01208655430236979</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Y51" t="n">
         <v>0.04750701294000544</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Z51" t="n">
         <v>0.02158792650918635</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AA51" t="n">
         <v>0.02888139263701483</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AB51" t="n">
         <v>0.1069623806850084</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
         <v>0.02388535031847134</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>0.06431578947368422</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AE51" t="n">
         <v>0.0251937984496124</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AF51" t="n">
         <v>0.02941176470588235</v>
       </c>
-      <c r="AE51" t="n">
+      <c r="AG51" t="n">
         <v>0.03955419580419581</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AH51" t="n">
         <v>0.04220588235294118</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -5844,104 +6354,114 @@
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>380.496</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>376.711</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>100</v>
       </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve"> The large triangle appears in the bottom, moves left, and bounces once.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>0.04000455373406193</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>0.03888888888888888</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>0.05570358810902847</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>0.02546296296296296</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>0.00574712643678161</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>0.05277544154751893</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>0.06095403383433309</v>
       </c>
-      <c r="O52" t="n">
+      <c r="Q52" t="n">
         <v>0.02803203661327231</v>
       </c>
-      <c r="P52" t="n">
+      <c r="R52" t="n">
         <v>0.08345565203392026</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="S52" t="n">
         <v>0.05121359055561603</v>
       </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>2</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
         <v>0.0423728813559322</v>
       </c>
-      <c r="T52" t="n">
+      <c r="V52" t="n">
         <v>0.06323051948051948</v>
       </c>
-      <c r="U52" t="n">
+      <c r="W52" t="n">
         <v>0.05599547511312217</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>0.04140127388535032</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Y52" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Z52" t="n">
         <v>0.1246688856528673</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AA52" t="n">
         <v>0.02586206896551724</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AB52" t="n">
         <v>0.118142394004463</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AC52" t="n">
         <v>0.08284991132131245</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AD52" t="n">
         <v>0.08501326259946951</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AE52" t="n">
         <v>0.03213635180848295</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AF52" t="n">
         <v>0.07584621044885945</v>
       </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>0.07268167840686925</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5949,67 +6469,71 @@
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>388.967</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>381.717</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>100</v>
       </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve"> The small triangle rotates 90 degrees, glides diagonally down, and bounces next to the large triangle.</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>0.04722222222222222</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>0.04123711340206185</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>0.05232558139534884</v>
       </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
         <v>0.04770318021201414</v>
       </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
         <v>0.04104477611940299</v>
       </c>
-      <c r="O53" t="n">
+      <c r="Q53" t="n">
         <v>0.05384615384615385</v>
       </c>
-      <c r="P53" t="n">
+      <c r="R53" t="n">
         <v>0.04207920792079208</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="S53" t="n">
         <v>0.07894415400400645</v>
       </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
       <c r="U53" t="n">
         <v>0</v>
       </c>
@@ -6017,36 +6541,42 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
         <v>0.08139534883720931</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Z53" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
         <v>0.1455486929939485</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AC53" t="n">
         <v>0.1029177594604721</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AD53" t="n">
         <v>0.1529230769230769</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AE53" t="n">
         <v>0.07497776083365104</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AF53" t="n">
         <v>0.07222222222222222</v>
       </c>
-      <c r="AE53" t="n">
+      <c r="AG53" t="n">
         <v>0.03365384615384615</v>
       </c>
-      <c r="AF53" t="n">
+      <c r="AH53" t="n">
         <v>0.1135585585585586</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -6054,104 +6584,114 @@
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>395.836</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>388.987</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>100</v>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve">  It slides out of the structure.  The structure reconfigures into a rectangle with a gap in the upper left side and a circle in the bottom left.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>0.05500000000000001</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>0.02580645161290323</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
         <v>0.02352941176470588</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>0.07055702917771883</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>0.04887780548628429</v>
       </c>
-      <c r="O54" t="n">
+      <c r="Q54" t="n">
         <v>0.07342268715266426</v>
       </c>
-      <c r="P54" t="n">
+      <c r="R54" t="n">
         <v>0.05560975609756098</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="S54" t="n">
         <v>0.07342287342287342</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
         <v>1</v>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
       <c r="U54" t="n">
         <v>0</v>
       </c>
       <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
         <v>0.1656050955414013</v>
       </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
         <v>0.1477832512315271</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AC54" t="n">
         <v>0.221105527638191</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AD54" t="n">
         <v>0.1862068965517241</v>
       </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
         <v>0.1589403973509934</v>
       </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.1450381679389313</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -6159,104 +6699,114 @@
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>405.689</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>396.416</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>100</v>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve">  The small triangle slides through the gap.  It touches the angled bar which rotates to close the gap.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>0.03848133848133849</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>0.03405797101449275</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>0.01132075471698113</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>0.04950166112956811</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>0.0910501362707245</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>0.04985050285403643</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>0.02269242025168276</v>
       </c>
-      <c r="O55" t="n">
+      <c r="Q55" t="n">
         <v>0.1017582417582417</v>
       </c>
-      <c r="P55" t="n">
+      <c r="R55" t="n">
         <v>0.01544401544401544</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="S55" t="n">
         <v>0.01611374407582938</v>
       </c>
-      <c r="R55" t="n">
+      <c r="T55" t="n">
         <v>1</v>
       </c>
-      <c r="S55" t="n">
+      <c r="U55" t="n">
         <v>0.07815126050420168</v>
       </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
       <c r="V55" t="n">
         <v>0</v>
       </c>
       <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
         <v>0.1018826135105205</v>
       </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AB55" t="n">
         <v>0.06569343065693431</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AC55" t="n">
         <v>0.118094220005048</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
         <v>0.1778380858734841</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AE55" t="n">
         <v>0.05424069881777229</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AF55" t="n">
         <v>0.0529595015576324</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="AG55" t="n">
         <v>0.0954878454878455</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AH55" t="n">
         <v>0.1057723577235772</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -6264,34 +6814,38 @@
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>415.718</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>406.61</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>100</v>
       </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve"> The triangle slides towards the circle until they are touching.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
@@ -6362,6 +6916,12 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6369,104 +6929,114 @@
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>427.528</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>421.803</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>100</v>
       </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">  The triangle moves towards the circle and the circle moves away.  A square appears on the left and moves towards the rectangle.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>0.03278688524590163</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>0.009090909090909089</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>0.0452479444359328</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>0.0169753086419753</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>0.003831417624521073</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>0.04914301856129011</v>
       </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
         <v>0.09514304354368998</v>
       </c>
-      <c r="O57" t="n">
+      <c r="Q57" t="n">
         <v>0.03872212500560865</v>
       </c>
-      <c r="P57" t="n">
+      <c r="R57" t="n">
         <v>0.1130841286673736</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="S57" t="n">
         <v>0.04764130065789191</v>
       </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>1.2</v>
       </c>
-      <c r="S57" t="n">
+      <c r="U57" t="n">
         <v>0.02824858757062147</v>
       </c>
-      <c r="T57" t="n">
+      <c r="V57" t="n">
         <v>0.07191558441558442</v>
       </c>
-      <c r="U57" t="n">
+      <c r="W57" t="n">
         <v>0.08634992458521872</v>
       </c>
-      <c r="V57" t="n">
+      <c r="X57" t="n">
         <v>0.02760084925690021</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Y57" t="n">
         <v>0.03737373737373737</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Z57" t="n">
         <v>0.112345534938603</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AA57" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AB57" t="n">
         <v>0.1725595359547615</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AC57" t="n">
         <v>0.07296203238414294</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AD57" t="n">
         <v>0.05597779341621706</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AE57" t="n">
         <v>0.0472411186696901</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AF57" t="n">
         <v>0.02649006622516556</v>
       </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0.05990838407916027</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -6474,104 +7044,114 @@
       <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>432.152</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>427.908</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>88.2</v>
       </c>
-      <c r="C58" t="n">
+      <c r="E58" t="n">
         <v>11.8</v>
       </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
         <v>-15.31</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t xml:space="preserve">  The square stops.  It touches the bar which rotates to make a gap.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>0.05952380952380953</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>0.06431159420289853</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>0.02830188679245283</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>0.1263910969793323</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
         <v>0.5</v>
       </c>
-      <c r="S58" t="n">
+      <c r="U58" t="n">
         <v>0.1</v>
       </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
       <c r="V58" t="n">
         <v>0</v>
       </c>
       <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AD58" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
       <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -6579,104 +7159,114 @@
       <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>439.287</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>433.718</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>100</v>
       </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t xml:space="preserve">  It moves to the triangle's position.  The shapes touch and then bounce adjacent to each other.</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>shapesphysical_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>0.02185792349726776</v>
       </c>
-      <c r="I59" t="n">
+      <c r="K59" t="n">
         <v>0.07879310344827585</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>0.0549461587913854</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>0.07059005251776336</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>0.01754385964912281</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>0.04445368637508375</v>
       </c>
-      <c r="N59" t="n">
+      <c r="P59" t="n">
         <v>0.04054054054054055</v>
       </c>
-      <c r="O59" t="n">
+      <c r="Q59" t="n">
         <v>0.04848484848484848</v>
       </c>
-      <c r="P59" t="n">
+      <c r="R59" t="n">
         <v>0.05314009661835748</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="S59" t="n">
         <v>0.02392460860313117</v>
       </c>
-      <c r="R59" t="n">
+      <c r="T59" t="n">
         <v>0.75</v>
       </c>
-      <c r="S59" t="n">
+      <c r="U59" t="n">
         <v>0.1224489795918367</v>
       </c>
-      <c r="T59" t="n">
+      <c r="V59" t="n">
         <v>0.09283562822719449</v>
       </c>
-      <c r="U59" t="n">
+      <c r="W59" t="n">
         <v>0.2273755656108598</v>
       </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
       <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
         <v>0.07106918238993711</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AA59" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AB59" t="n">
         <v>0.1153846153846154</v>
       </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
       <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
         <v>0.08904109589041095</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
         <v>0.1319444444444444</v>
       </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
       <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
         <v>0.4</v>
       </c>
     </row>
